--- a/RPA/데이터추출/리포트_1.xlsx
+++ b/RPA/데이터추출/리포트_1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3CLASS_010\OneDrive\Desktop\Mainproject\3team\RPA\데이터추출\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3CLASS_010\OneDrive\Desktop\3team\RPA\데이터추출\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCA840CD-D84A-4B38-8619-76DA43BD7436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCA5263E-F82D-42D1-A7D3-1EBCBB098B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2EAC96E0-CB8D-4D79-89EC-E141BB700244}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
   <si>
     <t>제목</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -52,51 +52,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>신한투자증권</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>알테오젠 콥데이 후기; 이제 알테오젠의 시간</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>2025.09.08</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1년간 주가를 눌러왔던 이슈들, 숫자 찍히면 달라진다
-할로자임 특허 문제로 다이이찌 산쿄 및 아스라제네카 L/O 성과는 주가에 전혀 반영되지 못해 저평가 판단. 최근 할로자임 86개 특허 청구항 포기로 이슈 해소. 키트루다SC 9/23 FDA승인 및 10/1 출시. KOSPI 이전과 연내 1~2건의 추가 계약. 4분기 실적으로 첫 인식될 판매 마일스톤으로 동사 매출과 이익 폭발적 상승 전망. 9월이 마지막 저평가 매수 기회될 것</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>씨어스테크놀로지 판매상 및 보험수가 시너지로 씽크 도입 확대 가속화</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>iM증권</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>진단지원 서비스 및 입원환자 모니터링 서비스 등을 제공하는 디지털 헬스케어 전문기업
-동사는 무선 웨어러블 의료기기와 의료 AI 기술을 바탕으로 심질환 진단 및 입원 환자 모니터링 서비스를 제공하는 디지털 헬스케어 전문기업이다. 즉, 생체신호 분석 인공지능 알고리즘과 웨어러블 의료기기를 활용한 IoMT(Internet of Medical Things) 플랫폼 기술을 기반으로 하여 국내외 의료기관을 대상으로 진단지원 서비스 모비케어(mobiCARE)와 입원환자 모니터링 서비스 씽크(thynC) 등을 제공하고 있다. 이를 통하여 병원 워크플로우 향상, 환자와 의료진 편의성 증대, 진료 수가를 기반한 병원 수익성 증대를 통해 의료서비스의 미충족 수요를 해결해 나가고 있다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>오리엔탈정공 LNG 운반선 관련 수주 확대로 실적개선 가속화</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>선박용 크레인 및 데크하우스 전문기업
-동사의 주요 제품군은 선용품과 기계류 부품 적재용 프로비전 크레인, 유조선의 오일호스 취급용 호스 핸들링 크레인, 벌크선용 데크 크레인 등이며, 주요 고객사는 국내 BIG3 조선소이다. 또한 동사의 자회사인 오리엔탈마린텍은 데크하우스와 엔진룸 케이싱 등을 주력으로 생산하고 있으며, 주요 고객사는 삼성중공업이다. 이러한 데크하우스는 선원들의 거주시설로서 각종 생활설비와 운항장비가 설치되는 대형 철 건축구조물이며 엔진룸 케이싱은 주기관, 보조기관, 발전기, 보일러 등 핵심 기계류가 설치되는 기관실의 외벽 구조물이다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>성광벤드 미국, 중동에서 LNG 관련 수주 증가로 실적개선 가속화</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>트럼프 2.0 시대 LNG 수출 터미널 허가 승인 가시화로 LNG 인프라 관련 기자재 수요 본격화 ⇒ 하반기 신규수주 가시화 되면서 성장성 가속화
-트럼프 2.0 시대 미국의 경우 글로벌 에너지 시장에서의 영향력 강화를 위한 핵심수단을 LNG에 두고 수출 확대를 위한 규제 완화를 가속화 하고 있다. 이에 따라 올해 1월 트럼프 대통령 취임과 동시에 미국 에너지 해방 행정명령을 발표하면서 바이든 정부 시절 중단되었던 신규 LNG 수출 허가를 전면 재개할 것을 에너지부(DOE)에 지시하였다. 이어 2월과 3월에는 커먼웰스(Commonwealth) LNG 수출 터미널 프로젝트와 CP2 LNG 수출 터미널 프로젝트에 대한 허가를 승인하였다. 무엇보다 LNG 수출 터미널 프로젝트에 대한 FID에서의 핵심 선결조건은 에너지부(DOE)의 수출 승인이다. 따라서 이와 같은 LNG 수출 터미널 프로젝트에 대한 허가 승인은 프로젝트의 상업성 확보로 인한 금융 조달, EPC 계약 체결 등 실질적인 사업 추진을 가능하게 하는 신호탄이 될 것이다. 다수의 프로젝트들이 향후 2~3년 내 FID 후 본격 투자 집행 단계에 진입할 것으로 예상됨에 따라 LNG 터미널 인프라를 중심으로 한 기자재 수요 등이 본격화 될 것이다. 이러한 환경하에서 동사의 경우 올해 하반기에 커먼웰스(Commonwealth) LNG 및 CP2 LNG 수출 터미널 프로젝트 관련 신규수주 등이 가시화 될 것으로 예상된다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -114,59 +70,124 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>덕산네오룩스 작년 연간 실적에 달하는 하반기 실적 예상</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>작년 연간 실적에 달하는 하반기 실적 기록하며 시장기대치 크게 상회할 전망
-동사의 하반기 실적은 시장 기대치를 크게 상회할 것으로 전망된다. OLED 소재는 계절적 성수기에 진입하면서 3Q25부터 아이폰17 신제품 출시 효과가 본격화되고, 4Q25에는 내년 2월 출시 예정인 갤럭시 S26 시리즈 출시 효과가 선반영되기 시작할 것으로 예상되기 때문이다. 특히 지난해 아이폰 프로/프로맥스 모델에만 한정되었던 삼성디스플레이의 M14 소재 구조가 올해는 아이폰 일반/에어 모델뿐만 아니라 갤럭시S26 시리즈까지 확대 적용될 예정이다. 특히 삼성전자의 폴더블 스마트폰에 이어 바타입 모델 중 처음으로 갤럭시 S26 울트라에 CoE(Color filter on encapsulation) 기술이 적용된다. 편광필름을 제거해 소비전력을 절감하고 투과율을 높이는 CoE 기술도입 확대는 동사가 독점 공급하는 블랙 PDL 수요를 확대시킬 것으로 기대된다. 이에 따라 기존 주력 공급소재인 HTL, 레드 프라임에 더해 그린 프라임과 블랙 PDL까지 매출 기여도가 확대되면서 실적 레버리지 효과가 가시화될 전망이다. 또한 중국 패널 업체들을 대상으로 한 신규 프로젝트 수주 증가와 연결 자회사인 현대중공업 터보기계의 3Q25 실적 개선도 긍정적인 요인이다. 이를 반영한 하반기 합산 매출액과 영업이익은 각각 2,322억원(+117% YoY), 510억원(+58% YoY)을 기록할 것으로 추정된다. 이는 작년 연간 실적에 달하는 수준이다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LG에너지솔루션 콥데이 후기; 방향성은 이상무</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ESS 호조 속 EV 경쟁력 강화
-미국 ESS 시장은 데이터센터 확대에 따른 전력 수요 증가 등으로 수요 고성장세 지속 전망. 중국산 배터리 고율관세(25년 40.9%, 26년 58.4%) 및 현지 생산 강점(유일한 ESS용 LFP 공급 업체)을 바탕으로 차별화된 경쟁력 부각. EV용 배터리는 유럽 내 점유율 하락 및 9월 이후 美 수요 둔화 우려 존재. 그럼에도 24년 이후 유럽&amp;북미향 8건의 수주를 통해 중장기 성장 모멘텀은 확대되고 있다는 판단</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>씨어스테크놀로지 Corp.day 후기; 의료 AI 수익화 선두</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>국내 의료 AI기업 중 가장 모범적인 수익화를 시현 중
-씽크 고성장이 주목받으며 연초대비 주가 크게 상승, 프리미엄 영역 도달. 추가적인 업사이드는 하반기 해외진출 성과가 좌우할 것으로 예상</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>엘앤케이바이오 콥데이 후기; 예열은 끝났다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>만년 후보에서 메이저 주전으로 승격 대기
-‘25년을 기점으로 고성장세 시작의 구체적인 계획과 전략 방향 제시. 미국 등 주요 시장 중심의 가시적인 성과가 도출되기 시작. 1) 척추부문은 글로벌 메이저 기업과 파트너십 진행, 척추 임플란트 주요 시장 공략, 2) 흉곽(PECTUS) 시장 개척, 거래처 확대가 외형 성장의 주요 핵심 포인트</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>메타바이오메드 탐방 後記: 숨겨진 저평가 실적주</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>유진투자증권</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I. 탐방 &amp; 3Q25 Preview
-- 1990 년 3 월 치과용 재료 제조 및 판매를 위한 메타치재산업사를 설립
-- 1999 년 7 월 ㈜메타치료로 법인 전환, 2001 년 6 월에 현재의 상호로 변경
-- 2008 년 4 월 한국증권서래소 코스닥 시장에 상장
-- 동사는 크게 덴탈 사업부, 봉합사 사업부 및 기타 사업으로 구분.
-- 치과 근관 치료 및 수복에 사용하는 근관 충전재 제품, 글로벌 M/S 20%, 1 위
-- 생체 분해성 봉합사 핵심기술 보유, 글로벌 7 개 업체가 과점
-- 국내외 2 개의 생산 거점, 4 개의 판매 거점을 구축. 국내 1 개 기술연구소 운용.
-- 미국, 독일, 중국, 일본 등을 중심으로 110 개국, 200 개 네트워크 보유</t>
+    <t>일동제약 주가 급락 코멘트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.09.03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>◎ Fact - 릴리, 경구 비만 치료제의 중단 소식
+&gt;&gt; 릴리의 차세대 경구용 GLP-1 후보 물질 나페리글리프론(Naperiglipron, LY3549492) 임상 일부 중단 소식이 국내에 확산되면서, 동사의 저분자 경구 비만 후보물질에 대한 우려로 주가 급락
+&gt;&gt; 릴리의 임상 중단 소식은 8/29일 제약 및 바이오텍 산업 전문 뉴스 매체 Endpoints News에 보도되며 알려짐.
+- BMI 22~25의 환자 대상 220명 모집 목표. 임상 시작일 2025/7/21. 환자모집 1명. 중단 결정.
+- 2형 당뇨를 앓고 있는 비만 또는 과체중 성인 환자 대상 150명 환자 모집 목표. 임상 시작일 2025/7/29. 환자모집 1명. 중단 결정.
+&gt;&gt; 릴리, 전략적 사업상의 이유(strategic business reasons)로 종료 결정. 과체중 성인 대상으로 체중 감량을 보기 위한 2상은 환자 모집 275명 완료되어 36주차 체중 감량 확인 중. ’26.4월 1차 종료되어 ’26.2Q 중으로 데이터 발표 예상.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>현대모비스 2025 CEO Investor Day 국내 NDR 후기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.09.02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기관투자자의 관심은 로보틱스 신사업 검증에 집중
+국내 NDR에 참여한 기관투자자 대부분은 현대모비스가 2025 CID에서 발표했던 선도 기술 중에서 집중적으로 휴머노이드 액추에이터 신사업 경쟁력을 검증하고자 했다. 반면 선도 기술로 함께 소개된 EMB, SBW는 이미 HL만도를 비롯한 경쟁사들이 수년 전부터 투자자에게 어필해왔던 기술력인 만큼 질의가 나오지 않았으며 오히려 현대모비스가 현재 개발 중인 휴머노이드용 액추에이터의 기술적, 원가구조 경쟁우위에 대한 구체적 근거 요구가 다수 있었다. 현대모비스는 2025 CID를 통해 글로벌 로봇 시장 성장 전망치와 함께 액추에이터가 휴머노이드 재료비의 60%를 차지할 주요 부품임을 제시했다. 그러나 HL만도, SNT모티브, 로보티즈 등의 국내 경쟁사 또는 중국계 휴머노이드 밸류체인 대비 현대모비스가 지니는 경쟁우위 및 글로벌 시장점유율 목표치가 부재했던 것이 아쉬우며 이는 NDR에서도 명확히 해소되지는 못한 영역이다. 여전히 로보틱스 신사업 관련 그룹사별 역할이 확정되지 못한 이유도 있다. 현재 현대모비스는 Boston Dynamics의 Tier1 업체로서 Atlas 양산용 액추에이터 수주를 기대하고 있으며 해당 프로젝트에서는 단순 부품 외주 제조사 역할이 아닌 양산 설계 단계부터 적극적인 개입을 목표하고 있다. 현대모비스가 양산 중인 MDPS 시스템과의 기술적 유사성을 바탕으로 연구개발과 원재료 소싱에 대한 진입장벽을 낮출 전망이며 수주 성공 시 양산 초기에는 품질 확보를 위해 외주생산이 아닌 미국 내 직접 생산 체제 구축이 유력해 보인다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>카카오 최대주주 지분의 가치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.09.01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>카카오 최대주주 구형 이슈
+카카오 최대주주에 대한 구형은 이해관계 측면에서 크게 2가지 변화의 축으로 작동할 것으로 판단한다. 첫번째는 구형과 투병에 따른 본인의 사업 동기부여 약화이며, 둘째 현재 카카오와 강결합을 맺고 있는 오픈AI 입장에서 해당 주주지분에 대한 취득 가능성을 배제할 수 없는 점이다. 오픈AI 측면에서 GPT-5 출시 이후 유저 데이터 및 프롬프트 성향 등에 의거한 개인별 커스텀 모델에 대한 중요도가 커졌다는 점과 경쟁사인 구글은 이미 검색 및 유튜브 등 소셜기반 유저 데이터를 연계해 AI 선두 입지를 강화하고 있는 등 프런티어 모델과 AGI 및 ASI 도달을 목표로 둘 오픈AI 입장에서 잠재 리스크 요인이 증가되고 있는 양상이다. 현재까지 오픈AI는 종합 세그먼트 유저 데이터보다 오픈소스 및 합성 데이터 등에 의존하여 모델을 강화 및 개선하는 프로세스를 밟아왔고, 동 측면 단점을 보완하고자 B2C 기반 유저 데이터를 폭넓게 확보한 카카오와 전략적 제휴를 한 것이며 향후 양사간 피드 및 자율형 에이전트에 기반한 광고 및 B2C 구독경제 성장으로 재무적 업사이드를 추구할 동기부여가 명확하다고 할 수 있다. 이는 손익 개선을 통한 FCF를 창출해야만 IPO 뿐만 아니라 최근 메타 등 경쟁사가 내부 인력을 막대한 조건으로 영입하는 것을 방어하고 기존 투자자의 의구심을 없애는 동시에 신규 자금을 더 높은 밸류에이션으로 유치할 수 있는 모든 과정에 구심점 역할을 할 수 있기 때문이다. 따라서 현재 카카오 최대주주의 구형을 기점으로 오픈AI는 카카오 지분에 대한 관심도를 더욱 높일 개연성이 있을 것으로 판단하며 시기적으로 9월중 오픈AI 서울 사무소 개소와 9월말로 관측되는 카카오 피드 서비스 출시 및 10월말에서 11월초로 관측되는 카카오와 오픈AI간의 공동 프로덕트 출시 등 양사간의 다양한 사업적 움직임을 전후로 해당 이슈는 지속적으로 회자될 것으로 판단한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로보티즈 증설을 위한 유상증자 결정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.08.29</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>◎ 8/28일 1,000억원 규모 주주배정 유상증자 결정
+&gt;&gt; 로보티즈가 8/28일 1,000억원 규모의 주주배정 유상증자를 결정
+&gt;&gt; 예정발행가는 74,100원, 11/4일에 발행가격 확정 예정
+&gt;&gt; 신주 예정 상장일은 12/1일
+&gt;&gt; 자금 활용 용도는 시설자금 600억원, 운영자금 400억원(신공장 운영 자금 등)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한라IMS 탄탄한 현재, 친환경으로 그리는 미래</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>계측부터 선박수리까지, 내실 있는 조선 기자재 회사
+한라IMS는 선박용 계측기 및 통제장치 등을 공급하는 조선 기자재 회사이다. 지난 '21년에는 광양사업장을 인수해 선박수리 부문도 진출하였다. 2Q25 기준 매출은 357억원(YoY +39.4%), 영업이익 62억원(YoY +55.4%) 기록하며 성장을 이어갔다. 전방산업의 호황이 지속적인 수주잔고 상승으로 이어지며 숫자로 반영되고 있고, 조선사들의 고부가 선박 건조 확대에 따른 단가 상승 등이 주 요인이다. 현재 월평균 100억원 가량 꾸준한 수주를 받고 있다. 1H25 기준 수주 잔고는 649억원이다. 종속회사로는 중국 법인이 존재하며, 동일한 제품을 생산하여 현지 조선소에 공급한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HD현대중공업 HD현대미포 합병 관련 코멘트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.08.28</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>◎ 8월 27일 장 마감 후 HD현대미포 합병 공시
+&gt;&gt; HD현대중공업(존속회사)와 HD현대미포(소멸회사)는 8월 27일 장 마감 후 합병 발표
+- 27일 기준 HD현대중공업 시가총액 46조 2,508억원, HD현대미포 시가총액 8조 6,275억원
+- 합병 기일은 25.12.1일, 신주 상장은 25.12.15일 예정
+- 합병비율은 HD현대미포 1주당 HD현대중공업 0.4059146주 배정, 합병 신주는 16,189,618주 추정
+&gt;&gt; 주식 매수 청구권 가격은 HD현대중공업 462,626원, HD현대미포 192,695원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>삼성전자 HBM 출하량 급증, 실적 서프라이즈 예상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.08.22</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3Q25 영업이익 9조원(+93%QoQ)으로 상향 조정
+삼성전자의 3Q25 실적이 매출액 82.6조원(+11%QoQ)과 영업이익 9.0조원(+93%QoQ)을 기록하며, 당사의 기존 전망치 및 시장 컨센서스를 상회할 전망이다. HBM의 출하량이 +107%QoQ 급증하며 당초 기대치를 넘어설 것으로 예상되고, 모바일 DRAM의 판매 가격이 +15%QoQ 급등하며 범용 DRAM의 수익성 개선에 기여할 것으로 판단되기 때문이다. 비메모리 부문 역시 엑시노스2500과 CIS 판매 증대 효과로 인해, 영업적자가 1.6조원 수준으로 크게 감소할 전망이다. 3Q25 사업 부문별 영업이익은 DS 4.2조원(+737%QoQ), SDC 1.3조원(+155%QoQ), MX/NW 3.2조원(+3%QoQ), VD/DA 0.3조원(+35%QoQ)을 각각 기록할 전망이다.
+ </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>엠플러스 차별화된 실적. 각형 투자 수혜도 주목</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상반기 영업이익 146억원(YoY 957%)
+동사는 1H25 매출액 828억원(YoY 105%), 영업이익 146억원(YoY 957%)을 기록했다. 기 수주한 높은 수익성의 수주잔고가 매출로 반영된 것에 기인한다. 동사는 23년 최대 실적 달성 이후에도 꾸준히 2,000억원 이상의 수주잔고를 기록하였으나, 전방 시장의 투자 감소 영향으로 예상대비 매출 인식이 늦게 반영되었다(24년 연간 매출액 1,287억원). Turn-key 수주 등을 통해 수익성이 높은 해외 고객사 매출 비중이 증가한 부문도 수익성 개선에 기여했다. 기존 국내 주요 고객사 매출 비중은 24년 50%에서 1H25 기준 30%로 낮아진 것으로 파악된다. </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>넥센타이어 NDR 후기: 하반기 기회 요인, 투자의견 상향</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025.08.19</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유럽 2공장 가동률 100% 달성 및 국내 RE 확대 기대
+23년 12월에 준공된 넥센타이어 유럽 2공장 가동률 상승세가 지속되고 있다. 25년 1분기말: 60%, 2분기말: 75% 수준으로 확인되며 올해 말 기준 100% 달성을 목표로 ramp-up 중이다. 3분기는 유럽에서 법적으로 보장된 2주 하계휴가로 인한 가동률 저하 계절성이 나타날 수 있겠으나 이는 이미 사업계획에 반영된 건이므로 증산에 차질은 없을 전망이다. 5월 3일부터 발효된 미국 자동차 부품 품목관세 여파로 경쟁사들이 기존 미국 수출 물량 일부를 유럽 수출로 선회하며 유럽 RE 시장 경쟁이 치열해지고 있지만 넥센타이어 유럽 2공장은 OE 중심으로 증산 중이기에 직접적인 영향은 크지 않을 전망이다. 특히 24년 12월에서 25년 12월로 순연됐던 유럽연합의 EUDR 적용 천연고무 규제 발효 리스크를 연말의 유럽 2공장 완전 가동 체제가 흡수할 것으로 기대된다. 주요 경쟁사들과는 달리 이미 24년 하반기에 선제적으로 EUDR 적용 천연고무를 투입하면서 제조원가 상승을 경험해봤던 넥센타이어는 연말에 유럽 2공장에서 발생할 규모의 경제 효과로 고정비를 절감함으로써 EUDR 적용 천연고무 투입에 따른 변동비 상승을 상쇄하는 전략을 펼치게 될 전망이다. 또한 규제 적용 시점 순연으로 인해 재고로 남아 있던 EUDR 적용 천연고무가 다시 생산 투입 및 매출 발생이 시작되면서 재무구조 역시 개선될 전망이다. 또한 금호타이어 광주공장 화재에 따른 국내 타이어 시장의 공급 공백으로 인해 넥센타이어는 2Q25부터 현대차/기아향 국내 OE 공급을 확대하기 시작했다. 하반기부터 넥센타이어 국내 RE 공급도 동반 확대될 것으로 판단하며 특히 창녕공장은 기존에 OE 비중이 높아 넥센타이어 글로벌 생산기지 중 가장 수익성이 낮았기에 국내 RE 공급 확대에 따른 실적 개선 효과가 기대된다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -537,10 +558,10 @@
   <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="66.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="52.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="88.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="99.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -557,144 +578,144 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="181.5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="148.5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="264" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="214.5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="132" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="264" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="379.5" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
